--- a/artfynd/A 54841-2022 artfynd.xlsx
+++ b/artfynd/A 54841-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54841-2022 artfynd.xlsx
+++ b/artfynd/A 54841-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7001636</v>
+        <v>110059288</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Hjd</t>
+          <t>Källstakojan, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424189.4614361324</v>
+        <v>424584</v>
       </c>
       <c r="R2" t="n">
-        <v>6967041.962459751</v>
+        <v>6966884</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7001641</v>
+        <v>7001635</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>423941.1091701119</v>
+        <v>424373</v>
       </c>
       <c r="R3" t="n">
-        <v>6967172.535847535</v>
+        <v>6967186</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +841,9 @@
           <t>2013-10-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7001640</v>
+        <v>7001637</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423926.0056635729</v>
+        <v>424189</v>
       </c>
       <c r="R4" t="n">
-        <v>6967192.546723344</v>
+        <v>6967042</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +942,9 @@
           <t>2013-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +978,7 @@
         <v>7001639</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424090.7260924286</v>
+        <v>424091</v>
       </c>
       <c r="R5" t="n">
-        <v>6967128.37712507</v>
+        <v>6967128</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1043,9 @@
           <t>2013-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7001637</v>
+        <v>7001640</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>424189.4614361324</v>
+        <v>423926</v>
       </c>
       <c r="R6" t="n">
-        <v>6967041.962459751</v>
+        <v>6967193</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1144,9 @@
           <t>2013-10-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7001635</v>
+        <v>7001641</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>424372.7277349495</v>
+        <v>423941</v>
       </c>
       <c r="R7" t="n">
-        <v>6967185.875737157</v>
+        <v>6967173</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1245,9 @@
           <t>2013-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,50 +1278,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7001638</v>
+        <v>110059178</v>
       </c>
       <c r="B8" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Vävelsjön, Hjd</t>
+          <t>Källstakojan, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>424090.7260924286</v>
+        <v>424606</v>
       </c>
       <c r="R8" t="n">
-        <v>6967128.37712507</v>
+        <v>6966828</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,22 +1344,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,31 +1364,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110059178</v>
+        <v>110059231</v>
       </c>
       <c r="B9" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>424606.2549412255</v>
+        <v>424600</v>
       </c>
       <c r="R9" t="n">
-        <v>6966827.964798736</v>
+        <v>6966862</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1561,19 +1445,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,51 +1474,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110059231</v>
+        <v>7001636</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källstakojan, Hjd</t>
+          <t>Stor-Vävelsjön, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>424599.7094306676</v>
+        <v>424189</v>
       </c>
       <c r="R10" t="n">
-        <v>6966861.952965301</v>
+        <v>6967042</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,22 +1539,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,27 +1559,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110059288</v>
+        <v>7001638</v>
       </c>
       <c r="B11" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,35 +1586,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källstakojan, Hjd</t>
+          <t>Stor-Vävelsjön, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>424584.6425335977</v>
+        <v>424091</v>
       </c>
       <c r="R11" t="n">
-        <v>6966883.790621095</v>
+        <v>6967128</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1784,22 +1640,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-10-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,27 +1660,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110059030</v>
+        <v>110059122</v>
       </c>
       <c r="B12" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,21 +1687,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1867,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>424680.3188041424</v>
+        <v>424668</v>
       </c>
       <c r="R12" t="n">
-        <v>6966743.039739181</v>
+        <v>6966854</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1900,19 +1745,9 @@
           <t>2023-06-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,6 +1771,202 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110059030</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Källstakojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>424680</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966743</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110059120</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Källstakojan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>424668</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6966854</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
